--- a/Datos limpios/Pricing diario/Histórico/Pricing diario histórico.xlsx
+++ b/Datos limpios/Pricing diario/Histórico/Pricing diario histórico.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3815"/>
+  <dimension ref="A1:H3822"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -97975,10 +97975,10 @@
         <v>4316.99</v>
       </c>
       <c r="G3754">
-        <v>60486.16</v>
+        <v>59947.69</v>
       </c>
       <c r="H3754">
-        <v>356129.04</v>
+        <v>355590.57</v>
       </c>
     </row>
     <row r="3755">
@@ -98729,10 +98729,10 @@
         <v>3401.69</v>
       </c>
       <c r="G3783">
-        <v>164434.48</v>
+        <v>164194.48</v>
       </c>
       <c r="H3783">
-        <v>438984.4300000001</v>
+        <v>438744.4300000001</v>
       </c>
     </row>
     <row r="3784">
@@ -99084,7 +99084,7 @@
         <v>23891.31</v>
       </c>
       <c r="D3797">
-        <v>70115.75</v>
+        <v>70085.70999999999</v>
       </c>
       <c r="E3797">
         <v>380373.22</v>
@@ -99096,7 +99096,7 @@
         <v>59917.52</v>
       </c>
       <c r="H3797">
-        <v>556071.9399999999</v>
+        <v>556041.9</v>
       </c>
     </row>
     <row r="3798">
@@ -99145,10 +99145,10 @@
         <v>12823.31</v>
       </c>
       <c r="G3799">
-        <v>70946.51000000001</v>
+        <v>70228.18000000001</v>
       </c>
       <c r="H3799">
-        <v>660755.2100000001</v>
+        <v>660036.8800000001</v>
       </c>
     </row>
     <row r="3800">
@@ -99269,7 +99269,7 @@
         <v>76440.70999999999</v>
       </c>
       <c r="E3804">
-        <v>353344.83</v>
+        <v>352987.37</v>
       </c>
       <c r="F3804">
         <v>1105.36</v>
@@ -99278,7 +99278,7 @@
         <v>159409.91</v>
       </c>
       <c r="H3804">
-        <v>614488.34</v>
+        <v>614130.88</v>
       </c>
     </row>
     <row r="3805">
@@ -99295,7 +99295,7 @@
         <v>81814.63</v>
       </c>
       <c r="E3805">
-        <v>333715.39</v>
+        <v>333295.39</v>
       </c>
       <c r="F3805">
         <v>2320.64</v>
@@ -99304,7 +99304,7 @@
         <v>148389.49</v>
       </c>
       <c r="H3805">
-        <v>598898.9</v>
+        <v>598478.9</v>
       </c>
     </row>
     <row r="3806">
@@ -99422,7 +99422,7 @@
         <v>12041.7</v>
       </c>
       <c r="D3810">
-        <v>55630.35</v>
+        <v>55615.44</v>
       </c>
       <c r="E3810">
         <v>98798.82000000001</v>
@@ -99434,7 +99434,7 @@
         <v>128284.08</v>
       </c>
       <c r="H3810">
-        <v>313930.99</v>
+        <v>313916.08</v>
       </c>
     </row>
     <row r="3811">
@@ -99451,7 +99451,7 @@
         <v>79089.73999999999</v>
       </c>
       <c r="E3811">
-        <v>119886.94</v>
+        <v>119826.94</v>
       </c>
       <c r="F3811">
         <v>505.52</v>
@@ -99460,7 +99460,7 @@
         <v>227439</v>
       </c>
       <c r="H3811">
-        <v>459570.79</v>
+        <v>459510.79</v>
       </c>
     </row>
     <row r="3812">
@@ -99483,10 +99483,10 @@
         <v>718.4299999999999</v>
       </c>
       <c r="G3812">
-        <v>174044.37</v>
+        <v>173559.93</v>
       </c>
       <c r="H3812">
-        <v>489231.41</v>
+        <v>488746.97</v>
       </c>
     </row>
     <row r="3813">
@@ -99503,16 +99503,16 @@
         <v>123090.15</v>
       </c>
       <c r="E3813">
-        <v>106076.55</v>
+        <v>106043.07</v>
       </c>
       <c r="F3813">
         <v>18464.95</v>
       </c>
       <c r="G3813">
-        <v>109590.62</v>
+        <v>107090.62</v>
       </c>
       <c r="H3813">
-        <v>411221.74</v>
+        <v>408688.26</v>
       </c>
     </row>
     <row r="3814">
@@ -99567,301 +99567,189 @@
         <v>320</v>
       </c>
     </row>
+    <row r="3816">
+      <c r="A3816" s="2">
+        <v>45950</v>
+      </c>
+      <c r="B3816">
+        <v>29450</v>
+      </c>
+      <c r="C3816">
+        <v>27042.03</v>
+      </c>
+      <c r="D3816">
+        <v>66628.43000000001</v>
+      </c>
+      <c r="E3816">
+        <v>74159.78</v>
+      </c>
+      <c r="F3816">
+        <v>631.89</v>
+      </c>
+      <c r="G3816">
+        <v>81259.23</v>
+      </c>
+      <c r="H3816">
+        <v>279171.36</v>
+      </c>
+    </row>
+    <row r="3817">
+      <c r="A3817" s="2">
+        <v>45951</v>
+      </c>
+      <c r="B3817">
+        <v>32388.12</v>
+      </c>
+      <c r="C3817">
+        <v>44079.39999999999</v>
+      </c>
+      <c r="D3817">
+        <v>84594.35000000001</v>
+      </c>
+      <c r="E3817">
+        <v>71878.75</v>
+      </c>
+      <c r="F3817">
+        <v>1088.84</v>
+      </c>
+      <c r="G3817">
+        <v>76019.7</v>
+      </c>
+      <c r="H3817">
+        <v>310049.16</v>
+      </c>
+    </row>
+    <row r="3818">
+      <c r="A3818" s="2">
+        <v>45952</v>
+      </c>
+      <c r="B3818">
+        <v>29730.26</v>
+      </c>
+      <c r="C3818">
+        <v>72299.75999999999</v>
+      </c>
+      <c r="D3818">
+        <v>63143.67</v>
+      </c>
+      <c r="E3818">
+        <v>63085.05</v>
+      </c>
+      <c r="F3818">
+        <v>1667.67</v>
+      </c>
+      <c r="G3818">
+        <v>89844.42000000001</v>
+      </c>
+      <c r="H3818">
+        <v>319770.83</v>
+      </c>
+    </row>
+    <row r="3819">
+      <c r="A3819" s="2">
+        <v>45953</v>
+      </c>
+      <c r="B3819">
+        <v>11516</v>
+      </c>
+      <c r="C3819">
+        <v>57566.02</v>
+      </c>
+      <c r="D3819">
+        <v>94249.38</v>
+      </c>
+      <c r="E3819">
+        <v>73422.39999999999</v>
+      </c>
+      <c r="F3819">
+        <v>3691.9</v>
+      </c>
+      <c r="G3819">
+        <v>88709.97</v>
+      </c>
+      <c r="H3819">
+        <v>329155.67</v>
+      </c>
+    </row>
+    <row r="3820">
+      <c r="A3820" s="2">
+        <v>45954</v>
+      </c>
+      <c r="B3820">
+        <v>15587.85</v>
+      </c>
+      <c r="C3820">
+        <v>48819.15</v>
+      </c>
+      <c r="D3820">
+        <v>96354.72</v>
+      </c>
+      <c r="E3820">
+        <v>123627.6</v>
+      </c>
+      <c r="F3820">
+        <v>684.49</v>
+      </c>
+      <c r="G3820">
+        <v>69403.23</v>
+      </c>
+      <c r="H3820">
+        <v>354477.04</v>
+      </c>
+    </row>
+    <row r="3821">
+      <c r="A3821" s="2">
+        <v>45955</v>
+      </c>
+      <c r="B3821">
+        <v>0</v>
+      </c>
+      <c r="C3821">
+        <v>30</v>
+      </c>
+      <c r="D3821">
+        <v>425.97</v>
+      </c>
+      <c r="E3821">
+        <v>61.36</v>
+      </c>
+      <c r="F3821">
+        <v>0</v>
+      </c>
+      <c r="G3821">
+        <v>381.65</v>
+      </c>
+      <c r="H3821">
+        <v>898.98</v>
+      </c>
+    </row>
+    <row r="3822">
+      <c r="A3822" s="2">
+        <v>45957</v>
+      </c>
+      <c r="B3822">
+        <v>7950</v>
+      </c>
+      <c r="C3822">
+        <v>950</v>
+      </c>
+      <c r="D3822">
+        <v>1510</v>
+      </c>
+      <c r="E3822">
+        <v>2677.84</v>
+      </c>
+      <c r="F3822">
+        <v>0</v>
+      </c>
+      <c r="G3822">
+        <v>960</v>
+      </c>
+      <c r="H3822">
+        <v>14047.84</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D6CA5EAACE9DA04D9E421A617A76D009" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="bac5de4a034fee97af64ba5a2822cd53">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77131357-5c03-45fa-a80b-b9111bb46cb1" xmlns:ns3="d3f11db4-a96c-41b4-b8ec-902c72f52048" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="027d3429df443898fbbc0b888682b5bf" ns2:_="" ns3:_="">
-    <xsd:import namespace="77131357-5c03-45fa-a80b-b9111bb46cb1"/>
-    <xsd:import namespace="d3f11db4-a96c-41b4-b8ec-902c72f52048"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="77131357-5c03-45fa-a80b-b9111bb46cb1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="20" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6ab20cb4-9c0f-41d2-89f3-02c382a657d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d3f11db4-a96c-41b4-b8ec-902c72f52048" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ac6aff7b-77d9-4645-af3f-7b0008d975fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d3f11db4-a96c-41b4-b8ec-902c72f52048">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d3f11db4-a96c-41b4-b8ec-902c72f52048" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5DA61A57-47D9-4073-8181-675E98E92D35}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EA78D3DE-97E0-4962-96DC-6AB9D5355B54}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9C1AF702-7D28-46D7-AFDC-84EC0595F810}"/>
 </file>
--- a/Datos limpios/Pricing diario/Histórico/Pricing diario histórico.xlsx
+++ b/Datos limpios/Pricing diario/Histórico/Pricing diario histórico.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3822"/>
+  <dimension ref="A1:H3847"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -98521,10 +98521,10 @@
         <v>5645.639999999999</v>
       </c>
       <c r="G3775">
-        <v>73682.87999999999</v>
+        <v>73542.2</v>
       </c>
       <c r="H3775">
-        <v>410059.26</v>
+        <v>409918.58</v>
       </c>
     </row>
     <row r="3776">
@@ -98729,10 +98729,10 @@
         <v>3401.69</v>
       </c>
       <c r="G3783">
-        <v>164194.48</v>
+        <v>164160.56</v>
       </c>
       <c r="H3783">
-        <v>438744.4300000001</v>
+        <v>438710.51</v>
       </c>
     </row>
     <row r="3784">
@@ -98853,7 +98853,7 @@
         <v>72983.32000000001</v>
       </c>
       <c r="E3788">
-        <v>481877.8100000001</v>
+        <v>480607.55</v>
       </c>
       <c r="F3788">
         <v>3468.49</v>
@@ -98862,7 +98862,7 @@
         <v>100670.96</v>
       </c>
       <c r="H3788">
-        <v>665943.84</v>
+        <v>664673.58</v>
       </c>
     </row>
     <row r="3789">
@@ -98885,10 +98885,10 @@
         <v>563.99</v>
       </c>
       <c r="G3789">
-        <v>162646.26</v>
+        <v>162458.53</v>
       </c>
       <c r="H3789">
-        <v>1706993.91</v>
+        <v>1706806.18</v>
       </c>
     </row>
     <row r="3790">
@@ -98905,16 +98905,16 @@
         <v>206389.3</v>
       </c>
       <c r="E3790">
-        <v>1574424.4</v>
+        <v>1574405.94</v>
       </c>
       <c r="F3790">
         <v>1872.14</v>
       </c>
       <c r="G3790">
-        <v>161099.2</v>
+        <v>160099.2</v>
       </c>
       <c r="H3790">
-        <v>2042044.69</v>
+        <v>2041026.23</v>
       </c>
     </row>
     <row r="3791">
@@ -98931,7 +98931,7 @@
         <v>152926.75</v>
       </c>
       <c r="E3791">
-        <v>837417.1100000001</v>
+        <v>837359.4</v>
       </c>
       <c r="F3791">
         <v>5454.65</v>
@@ -98940,7 +98940,7 @@
         <v>106359.36</v>
       </c>
       <c r="H3791">
-        <v>1144108.5</v>
+        <v>1144050.79</v>
       </c>
     </row>
     <row r="3792">
@@ -99087,16 +99087,16 @@
         <v>70085.70999999999</v>
       </c>
       <c r="E3797">
-        <v>380373.22</v>
+        <v>380369.38</v>
       </c>
       <c r="F3797">
         <v>11864.14</v>
       </c>
       <c r="G3797">
-        <v>59917.52</v>
+        <v>59796.03</v>
       </c>
       <c r="H3797">
-        <v>556041.9</v>
+        <v>555916.5700000001</v>
       </c>
     </row>
     <row r="3798">
@@ -99113,7 +99113,7 @@
         <v>92329.42</v>
       </c>
       <c r="E3798">
-        <v>370912.65</v>
+        <v>370765.3</v>
       </c>
       <c r="F3798">
         <v>1132.62</v>
@@ -99122,7 +99122,7 @@
         <v>69660.97</v>
       </c>
       <c r="H3798">
-        <v>557229.26</v>
+        <v>557081.91</v>
       </c>
     </row>
     <row r="3799">
@@ -99139,16 +99139,16 @@
         <v>90230.02000000002</v>
       </c>
       <c r="E3799">
-        <v>423023.69</v>
+        <v>423024.43</v>
       </c>
       <c r="F3799">
         <v>12823.31</v>
       </c>
       <c r="G3799">
-        <v>70228.18000000001</v>
+        <v>69938.09000000001</v>
       </c>
       <c r="H3799">
-        <v>660036.8800000001</v>
+        <v>659747.53</v>
       </c>
     </row>
     <row r="3800">
@@ -99217,7 +99217,7 @@
         <v>97668.79000000001</v>
       </c>
       <c r="E3802">
-        <v>227120.04</v>
+        <v>227000.04</v>
       </c>
       <c r="F3802">
         <v>1361.07</v>
@@ -99226,7 +99226,7 @@
         <v>83410.52</v>
       </c>
       <c r="H3802">
-        <v>427881.6800000001</v>
+        <v>427761.6800000001</v>
       </c>
     </row>
     <row r="3803">
@@ -99249,10 +99249,10 @@
         <v>994.22</v>
       </c>
       <c r="G3803">
-        <v>87765.79000000001</v>
+        <v>87610.52</v>
       </c>
       <c r="H3803">
-        <v>420817.7</v>
+        <v>420662.43</v>
       </c>
     </row>
     <row r="3804">
@@ -99405,10 +99405,10 @@
         <v>901.3099999999999</v>
       </c>
       <c r="G3809">
-        <v>137133.03</v>
+        <v>136836.47</v>
       </c>
       <c r="H3809">
-        <v>324046.59</v>
+        <v>323750.03</v>
       </c>
     </row>
     <row r="3810">
@@ -99506,13 +99506,13 @@
         <v>106043.07</v>
       </c>
       <c r="F3813">
-        <v>18464.95</v>
+        <v>17464.95</v>
       </c>
       <c r="G3813">
         <v>107090.62</v>
       </c>
       <c r="H3813">
-        <v>408688.26</v>
+        <v>407688.26</v>
       </c>
     </row>
     <row r="3814">
@@ -99728,25 +99728,675 @@
         <v>45957</v>
       </c>
       <c r="B3822">
-        <v>7950</v>
+        <v>19388.34</v>
       </c>
       <c r="C3822">
-        <v>950</v>
+        <v>18330.34</v>
       </c>
       <c r="D3822">
-        <v>1510</v>
+        <v>64599.99000000001</v>
       </c>
       <c r="E3822">
-        <v>2677.84</v>
+        <v>56853.16</v>
       </c>
       <c r="F3822">
-        <v>0</v>
+        <v>1289.08</v>
       </c>
       <c r="G3822">
-        <v>960</v>
+        <v>50675.54</v>
       </c>
       <c r="H3822">
-        <v>14047.84</v>
+        <v>211136.45</v>
+      </c>
+    </row>
+    <row r="3823">
+      <c r="A3823" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B3823">
+        <v>18221.26</v>
+      </c>
+      <c r="C3823">
+        <v>11008.73</v>
+      </c>
+      <c r="D3823">
+        <v>117118.26</v>
+      </c>
+      <c r="E3823">
+        <v>118743.84</v>
+      </c>
+      <c r="F3823">
+        <v>1556.12</v>
+      </c>
+      <c r="G3823">
+        <v>102356.76</v>
+      </c>
+      <c r="H3823">
+        <v>369004.97</v>
+      </c>
+    </row>
+    <row r="3824">
+      <c r="A3824" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B3824">
+        <v>11773</v>
+      </c>
+      <c r="C3824">
+        <v>10770.94</v>
+      </c>
+      <c r="D3824">
+        <v>95470.38</v>
+      </c>
+      <c r="E3824">
+        <v>58551.82</v>
+      </c>
+      <c r="F3824">
+        <v>1664.4</v>
+      </c>
+      <c r="G3824">
+        <v>62442.2</v>
+      </c>
+      <c r="H3824">
+        <v>240672.74</v>
+      </c>
+    </row>
+    <row r="3825">
+      <c r="A3825" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B3825">
+        <v>21536.23</v>
+      </c>
+      <c r="C3825">
+        <v>11518.56</v>
+      </c>
+      <c r="D3825">
+        <v>130203.01</v>
+      </c>
+      <c r="E3825">
+        <v>55796.11</v>
+      </c>
+      <c r="F3825">
+        <v>892.0599999999999</v>
+      </c>
+      <c r="G3825">
+        <v>92197.7</v>
+      </c>
+      <c r="H3825">
+        <v>312143.67</v>
+      </c>
+    </row>
+    <row r="3826">
+      <c r="A3826" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B3826">
+        <v>31360</v>
+      </c>
+      <c r="C3826">
+        <v>8032.99</v>
+      </c>
+      <c r="D3826">
+        <v>146743.22</v>
+      </c>
+      <c r="E3826">
+        <v>48408.11</v>
+      </c>
+      <c r="F3826">
+        <v>7660.339999999999</v>
+      </c>
+      <c r="G3826">
+        <v>90562.22000000002</v>
+      </c>
+      <c r="H3826">
+        <v>332766.88</v>
+      </c>
+    </row>
+    <row r="3827">
+      <c r="A3827" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B3827">
+        <v>0</v>
+      </c>
+      <c r="C3827">
+        <v>0</v>
+      </c>
+      <c r="D3827">
+        <v>159.87</v>
+      </c>
+      <c r="E3827">
+        <v>2215.14</v>
+      </c>
+      <c r="F3827">
+        <v>0</v>
+      </c>
+      <c r="G3827">
+        <v>1597.81</v>
+      </c>
+      <c r="H3827">
+        <v>3972.82</v>
+      </c>
+    </row>
+    <row r="3828">
+      <c r="A3828" s="2">
+        <v>45963</v>
+      </c>
+      <c r="B3828">
+        <v>0</v>
+      </c>
+      <c r="C3828">
+        <v>0</v>
+      </c>
+      <c r="D3828">
+        <v>0</v>
+      </c>
+      <c r="E3828">
+        <v>13081.43</v>
+      </c>
+      <c r="F3828">
+        <v>0</v>
+      </c>
+      <c r="G3828">
+        <v>0</v>
+      </c>
+      <c r="H3828">
+        <v>13081.43</v>
+      </c>
+    </row>
+    <row r="3829">
+      <c r="A3829" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B3829">
+        <v>26455.8</v>
+      </c>
+      <c r="C3829">
+        <v>8996.65</v>
+      </c>
+      <c r="D3829">
+        <v>137256.09</v>
+      </c>
+      <c r="E3829">
+        <v>81738.89999999999</v>
+      </c>
+      <c r="F3829">
+        <v>2699.28</v>
+      </c>
+      <c r="G3829">
+        <v>99453.11</v>
+      </c>
+      <c r="H3829">
+        <v>356599.83</v>
+      </c>
+    </row>
+    <row r="3830">
+      <c r="A3830" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B3830">
+        <v>41360.75999999999</v>
+      </c>
+      <c r="C3830">
+        <v>31218.63</v>
+      </c>
+      <c r="D3830">
+        <v>100755.44</v>
+      </c>
+      <c r="E3830">
+        <v>107688.57</v>
+      </c>
+      <c r="F3830">
+        <v>1710.15</v>
+      </c>
+      <c r="G3830">
+        <v>77600.31999999999</v>
+      </c>
+      <c r="H3830">
+        <v>360333.8700000001</v>
+      </c>
+    </row>
+    <row r="3831">
+      <c r="A3831" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B3831">
+        <v>20673.65</v>
+      </c>
+      <c r="C3831">
+        <v>22130.88</v>
+      </c>
+      <c r="D3831">
+        <v>295755.66</v>
+      </c>
+      <c r="E3831">
+        <v>42870.54</v>
+      </c>
+      <c r="F3831">
+        <v>4628.26</v>
+      </c>
+      <c r="G3831">
+        <v>95292.70000000001</v>
+      </c>
+      <c r="H3831">
+        <v>481351.6900000001</v>
+      </c>
+    </row>
+    <row r="3832">
+      <c r="A3832" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B3832">
+        <v>12292.76</v>
+      </c>
+      <c r="C3832">
+        <v>-5764.84</v>
+      </c>
+      <c r="D3832">
+        <v>212826.47</v>
+      </c>
+      <c r="E3832">
+        <v>111236.27</v>
+      </c>
+      <c r="F3832">
+        <v>1946.28</v>
+      </c>
+      <c r="G3832">
+        <v>71152.63</v>
+      </c>
+      <c r="H3832">
+        <v>403689.57</v>
+      </c>
+    </row>
+    <row r="3833">
+      <c r="A3833" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B3833">
+        <v>23785.06</v>
+      </c>
+      <c r="C3833">
+        <v>9313.780000000001</v>
+      </c>
+      <c r="D3833">
+        <v>127060.58</v>
+      </c>
+      <c r="E3833">
+        <v>127863.62</v>
+      </c>
+      <c r="F3833">
+        <v>2209.08</v>
+      </c>
+      <c r="G3833">
+        <v>61774.31</v>
+      </c>
+      <c r="H3833">
+        <v>352006.43</v>
+      </c>
+    </row>
+    <row r="3834">
+      <c r="A3834" s="2">
+        <v>45969</v>
+      </c>
+      <c r="B3834">
+        <v>0</v>
+      </c>
+      <c r="C3834">
+        <v>15</v>
+      </c>
+      <c r="D3834">
+        <v>516.72</v>
+      </c>
+      <c r="E3834">
+        <v>1378.62</v>
+      </c>
+      <c r="F3834">
+        <v>0</v>
+      </c>
+      <c r="G3834">
+        <v>254.2</v>
+      </c>
+      <c r="H3834">
+        <v>2164.54</v>
+      </c>
+    </row>
+    <row r="3835">
+      <c r="A3835" s="2">
+        <v>45970</v>
+      </c>
+      <c r="B3835">
+        <v>0</v>
+      </c>
+      <c r="C3835">
+        <v>0</v>
+      </c>
+      <c r="D3835">
+        <v>35</v>
+      </c>
+      <c r="E3835">
+        <v>500</v>
+      </c>
+      <c r="F3835">
+        <v>0</v>
+      </c>
+      <c r="G3835">
+        <v>0</v>
+      </c>
+      <c r="H3835">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="3836">
+      <c r="A3836" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B3836">
+        <v>14799.99</v>
+      </c>
+      <c r="C3836">
+        <v>8460.230000000001</v>
+      </c>
+      <c r="D3836">
+        <v>147347.01</v>
+      </c>
+      <c r="E3836">
+        <v>51602.62</v>
+      </c>
+      <c r="F3836">
+        <v>2021.14</v>
+      </c>
+      <c r="G3836">
+        <v>92511.98000000001</v>
+      </c>
+      <c r="H3836">
+        <v>316742.97</v>
+      </c>
+    </row>
+    <row r="3837">
+      <c r="A3837" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B3837">
+        <v>22060.6</v>
+      </c>
+      <c r="C3837">
+        <v>15913.23</v>
+      </c>
+      <c r="D3837">
+        <v>187223.45</v>
+      </c>
+      <c r="E3837">
+        <v>68845.47</v>
+      </c>
+      <c r="F3837">
+        <v>1437.55</v>
+      </c>
+      <c r="G3837">
+        <v>92712.08</v>
+      </c>
+      <c r="H3837">
+        <v>388192.38</v>
+      </c>
+    </row>
+    <row r="3838">
+      <c r="A3838" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B3838">
+        <v>10481.56</v>
+      </c>
+      <c r="C3838">
+        <v>11562.86</v>
+      </c>
+      <c r="D3838">
+        <v>122982.8</v>
+      </c>
+      <c r="E3838">
+        <v>85335.42000000001</v>
+      </c>
+      <c r="F3838">
+        <v>1078.46</v>
+      </c>
+      <c r="G3838">
+        <v>109947.54</v>
+      </c>
+      <c r="H3838">
+        <v>341388.64</v>
+      </c>
+    </row>
+    <row r="3839">
+      <c r="A3839" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B3839">
+        <v>15739.25</v>
+      </c>
+      <c r="C3839">
+        <v>9993.230000000001</v>
+      </c>
+      <c r="D3839">
+        <v>195224.96</v>
+      </c>
+      <c r="E3839">
+        <v>75975.76999999999</v>
+      </c>
+      <c r="F3839">
+        <v>1881.48</v>
+      </c>
+      <c r="G3839">
+        <v>145746.27</v>
+      </c>
+      <c r="H3839">
+        <v>444560.96</v>
+      </c>
+    </row>
+    <row r="3840">
+      <c r="A3840" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B3840">
+        <v>14622.57</v>
+      </c>
+      <c r="C3840">
+        <v>10007.08</v>
+      </c>
+      <c r="D3840">
+        <v>359640.37</v>
+      </c>
+      <c r="E3840">
+        <v>51099.35</v>
+      </c>
+      <c r="F3840">
+        <v>1177.15</v>
+      </c>
+      <c r="G3840">
+        <v>159314.17</v>
+      </c>
+      <c r="H3840">
+        <v>595860.6900000001</v>
+      </c>
+    </row>
+    <row r="3841">
+      <c r="A3841" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B3841">
+        <v>0</v>
+      </c>
+      <c r="C3841">
+        <v>0</v>
+      </c>
+      <c r="D3841">
+        <v>1776.47</v>
+      </c>
+      <c r="E3841">
+        <v>180</v>
+      </c>
+      <c r="F3841">
+        <v>145</v>
+      </c>
+      <c r="G3841">
+        <v>720</v>
+      </c>
+      <c r="H3841">
+        <v>2821.47</v>
+      </c>
+    </row>
+    <row r="3842">
+      <c r="A3842" s="2">
+        <v>45977</v>
+      </c>
+      <c r="B3842">
+        <v>0</v>
+      </c>
+      <c r="C3842">
+        <v>800.28</v>
+      </c>
+      <c r="D3842">
+        <v>0</v>
+      </c>
+      <c r="E3842">
+        <v>500</v>
+      </c>
+      <c r="F3842">
+        <v>0</v>
+      </c>
+      <c r="G3842">
+        <v>0</v>
+      </c>
+      <c r="H3842">
+        <v>1300.28</v>
+      </c>
+    </row>
+    <row r="3843">
+      <c r="A3843" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B3843">
+        <v>31748.74</v>
+      </c>
+      <c r="C3843">
+        <v>8849.66</v>
+      </c>
+      <c r="D3843">
+        <v>113945.08</v>
+      </c>
+      <c r="E3843">
+        <v>74008.22</v>
+      </c>
+      <c r="F3843">
+        <v>743.95</v>
+      </c>
+      <c r="G3843">
+        <v>113416.33</v>
+      </c>
+      <c r="H3843">
+        <v>342711.98</v>
+      </c>
+    </row>
+    <row r="3844">
+      <c r="A3844" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B3844">
+        <v>27423.37</v>
+      </c>
+      <c r="C3844">
+        <v>6666.099999999999</v>
+      </c>
+      <c r="D3844">
+        <v>80879.83</v>
+      </c>
+      <c r="E3844">
+        <v>102518.02</v>
+      </c>
+      <c r="F3844">
+        <v>480</v>
+      </c>
+      <c r="G3844">
+        <v>116519.79</v>
+      </c>
+      <c r="H3844">
+        <v>334487.11</v>
+      </c>
+    </row>
+    <row r="3845">
+      <c r="A3845" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B3845">
+        <v>27056</v>
+      </c>
+      <c r="C3845">
+        <v>15932.94</v>
+      </c>
+      <c r="D3845">
+        <v>113818.39</v>
+      </c>
+      <c r="E3845">
+        <v>97366.82999999999</v>
+      </c>
+      <c r="F3845">
+        <v>462.46</v>
+      </c>
+      <c r="G3845">
+        <v>136266.54</v>
+      </c>
+      <c r="H3845">
+        <v>390903.16</v>
+      </c>
+    </row>
+    <row r="3846">
+      <c r="A3846" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B3846">
+        <v>29415.74</v>
+      </c>
+      <c r="C3846">
+        <v>9690.279999999999</v>
+      </c>
+      <c r="D3846">
+        <v>68768.36</v>
+      </c>
+      <c r="E3846">
+        <v>66451.56</v>
+      </c>
+      <c r="F3846">
+        <v>2027.73</v>
+      </c>
+      <c r="G3846">
+        <v>100749.12</v>
+      </c>
+      <c r="H3846">
+        <v>277102.79</v>
+      </c>
+    </row>
+    <row r="3847">
+      <c r="A3847" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B3847">
+        <v>10210</v>
+      </c>
+      <c r="C3847">
+        <v>2256.3</v>
+      </c>
+      <c r="D3847">
+        <v>7049.309999999999</v>
+      </c>
+      <c r="E3847">
+        <v>11084.31</v>
+      </c>
+      <c r="F3847">
+        <v>0</v>
+      </c>
+      <c r="G3847">
+        <v>20391.37</v>
+      </c>
+      <c r="H3847">
+        <v>50991.29</v>
       </c>
     </row>
   </sheetData>
